--- a/ig/175-upgrade-app-profiles/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/175-upgrade-app-profiles/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-14T10:16:17+00:00</t>
+    <t>2024-02-14T11:10:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -19246,7 +19246,7 @@
         <v>74</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>82</v>
@@ -20170,7 +20170,7 @@
         <v>74</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>82</v>
@@ -22636,7 +22636,7 @@
         <v>74</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>73</v>
